--- a/Zinc/6. Statistical data analysis/Multiple linear regression/Simple_MLR2.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/Simple_MLR2.xlsx
@@ -417,16 +417,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.000000000000000077190347216357</v>
+        <v>-0.00000000000000135493406020617</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0157862060350825</v>
+        <v>0.0156078337744125</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00000000000000488973392623996</v>
+        <v>-0.0000000000000868111539237081</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999999999999996</v>
+        <v>0.999999999999931</v>
       </c>
     </row>
     <row r="3">
@@ -434,16 +434,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.904546926581464</v>
+        <v>0.890732899726712</v>
       </c>
       <c r="C3" t="n">
-        <v>0.016385646193425</v>
+        <v>0.0161764653197066</v>
       </c>
       <c r="D3" t="n">
-        <v>55.2036163788541</v>
+        <v>55.0635062804232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000411483410306083</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000174079610545101</v>
       </c>
     </row>
     <row r="4">
@@ -451,16 +451,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.449988187116628</v>
+        <v>-0.48284429284374</v>
       </c>
       <c r="C4" t="n">
-        <v>0.017574398234445</v>
+        <v>0.0174228368781974</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.6047564823398</v>
+        <v>-27.7132992875552</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000026373563269168</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000235185279889239</v>
       </c>
     </row>
     <row r="5">
@@ -468,16 +468,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.315922438848736</v>
+        <v>-0.31010986692176</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0404856350716436</v>
+        <v>0.0409081289221567</v>
       </c>
       <c r="D5" t="n">
-        <v>-7.8033218026512</v>
+        <v>-7.58064167422232</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000000000000698578873871276</v>
+        <v>0.000000000000264622082493218</v>
       </c>
     </row>
     <row r="6">
@@ -485,16 +485,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0778262285150938</v>
+        <v>-0.0811625256555628</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0402779222274989</v>
+        <v>0.0410588751668798</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.93223046798476</v>
+        <v>-1.97673524483283</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0541354992569956</v>
+        <v>0.0487922373417426</v>
       </c>
     </row>
   </sheetData>
@@ -521,7 +521,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.297853539763453</v>
+        <v>0.306645279435475</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +529,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>0.912282893990095</v>
+        <v>0.906945621456044</v>
       </c>
     </row>
     <row r="4">
@@ -537,7 +537,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="n">
-        <v>0.911283268850381</v>
+        <v>0.905968672599939</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>912.625000858911</v>
+        <v>928.345036476512</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
